--- a/apps/ceo1983_app_fe/public/docs/TEST_CASES_HE_THONG_CEO1983.xlsx
+++ b/apps/ceo1983_app_fe/public/docs/TEST_CASES_HE_THONG_CEO1983.xlsx
@@ -179,26 +179,23 @@
     <t>UC-PUB-05</t>
   </si>
   <si>
-    <t>Tra Cứu Trực Tuyến Tiến Độ Thẩm Định Hồ Sơ Gia Nhập CLB CEO 1983</t>
-  </si>
-  <si>
-    <t>Ứng viên gia nhập CLB</t>
-  </si>
-  <si>
-    <t>Ứng viên đã nộp đơn đăng ký và có mã hồ sơ hoặc email đăng ký.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Ứng viên truy cập mục "Tra Cứu Hồ Sơ" trên Cổng thông tin điện tử.
-2. Nhập địa chỉ email: vupv090120@gmail.com hoặc Số điện thoại: 0901201983.
-3. Bấm "Tra Cứu Tiến Độ".
-4. Màn hình hiển thị dòng thời gian xử lý trực quan:
-   - Bước 1: Tiếp nhận hồ sơ trực tuyến (Đã hoàn thành)
-   - Bước 2: Thẩm định hồ sơ doanh nghiệp bởi Ban Thành Viên (Đang thực hiện)
-   - Bước 3: Phê duyệt kết nạp &amp; Cấp mã Hội viên CEO-83xxx
-   - Bước 4: Kích hoạt tài khoản và Thẻ Doanh nhân VIP 3D NFC.</t>
-  </si>
-  <si>
-    <t>Ứng viên theo dõi được minh bạch tiến độ xét duyệt của Ban Điều Hành CLB.</t>
+    <t>Gửi Thành Công Đơn Đăng Ký Gia Nhập &amp; Xác Nhận Tiếp Nhận Vào Hệ Thống Thẩm Định</t>
+  </si>
+  <si>
+    <t>Doanh nhân ứng viên (Đại diện: Doanh nhân Phạm Văn Vũ - vupv090120@gmail.com)</t>
+  </si>
+  <si>
+    <t>Ứng viên đã điền đầy đủ thông tin biểu mẫu tại Cổng Đăng Ký Gia Nhập Trực Tuyến và nhấn nút nộp hồ sơ.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Ứng viên nhấn nút "Gửi Hồ Sơ Đăng Ký Gia Nhập" trên Cổng thông tin điện tử tiếp nhận hồ sơ.
+2. Hệ thống kiểm tra tính hợp lệ của dữ liệu: Định dạng email, số điện thoại, ngày sinh 1983, tên doanh nghiệp và mã số thuế.
+3. Hệ thống tạo bản ghi mới trong bảng dữ liệu thành viên với trạng thái Chờ thẩm định (pending).
+4. Màn hình hiển thị thông điệp xác nhận trang trọng: "Đăng Ký Thành Công! Hồ sơ của Quý Doanh Nhân đã được chuyển trực tiếp tới Ban Thành Viên CLB Doanh Nhân CEO 1983 để thẩm định theo Quy chế kết nạp".
+5. Dữ liệu hồ sơ tự động đồng bộ sang phân hệ Quản Trị Hội Viên (Tab Chờ thẩm định) trên Cổng Quản Trị CRM dành cho Ban Thành Viên và Ban Quản Trị.</t>
+  </si>
+  <si>
+    <t>Hồ sơ đăng ký gia nhập được lưu trữ an toàn trong cơ sở dữ liệu và sẵn sàng để Ban Thành Viên thẩm định trên Cổng CRM.</t>
   </si>
   <si>
     <t>sub_04_landing_status_polling.png</t>
@@ -3872,7 +3869,7 @@
     <t>Xây dựng môi trường giao thương nội bộ trung thực, tôn vinh các doanh nghiệp uy tín hàng đầu trong CLB.</t>
   </si>
   <si>
-    <t>app1983_10_marketplace_b2b.png</t>
+    <t>app1983_10_marketplace_shopee.png</t>
   </si>
   <si>
     <t>TC-130</t>
